--- a/TS Jatai Ghanam Project/Stas table for TS 4.1 TO 4.7.xlsx
+++ b/TS Jatai Ghanam Project/Stas table for TS 4.1 TO 4.7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ALL IMP DATA\GitHub\texts\TS Jatai Ghanam Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\texts\TS Jatai Ghanam Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F717547-F1C5-4EDD-A44C-824F64AC2EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4.1" sheetId="15" r:id="rId1"/>
@@ -22,10 +22,19 @@
     <sheet name="4.7" sheetId="21" r:id="rId7"/>
     <sheet name="total 4.1 to 4.7" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1695,7 +1704,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="fill"/>
@@ -1759,9 +1768,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -14186,7 +14192,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="2:11" ht="102" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:11" ht="89.25" x14ac:dyDescent="0.2">
       <c r="B2" s="6" t="s">
         <v>18</v>
       </c>
@@ -14216,7 +14222,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B3" s="11" t="s">
         <v>23</v>
       </c>
@@ -14249,7 +14255,7 @@
         <v>11189</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B4" s="11" t="s">
         <v>24</v>
       </c>
@@ -14304,7 +14310,7 @@
       <c r="H5" s="12">
         <v>197</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="12">
         <v>372</v>
       </c>
       <c r="J5" s="12">
@@ -14348,7 +14354,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B7" s="11" t="s">
         <v>27</v>
       </c>
@@ -14370,7 +14376,7 @@
       <c r="H7" s="12">
         <v>0</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="12">
         <v>9</v>
       </c>
       <c r="J7" s="12">
@@ -14483,7 +14489,7 @@
       </c>
     </row>
     <row r="14" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="27" t="s">
         <v>318</v>
       </c>
       <c r="C14" s="10" t="s">
@@ -14516,7 +14522,7 @@
       </c>
     </row>
     <row r="15" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="27" t="s">
         <v>319</v>
       </c>
       <c r="C15" s="10" t="s">
@@ -14549,7 +14555,7 @@
       </c>
     </row>
     <row r="16" spans="2:11" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="27" t="s">
         <v>320</v>
       </c>
       <c r="C16" s="10" t="s">
@@ -14582,7 +14588,7 @@
       </c>
     </row>
     <row r="17" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="27" t="s">
         <v>321</v>
       </c>
       <c r="C17" s="10" t="s">
@@ -14615,7 +14621,7 @@
       </c>
     </row>
     <row r="18" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="27" t="s">
         <v>322</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -14747,8 +14753,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="24.75" x14ac:dyDescent="0.6">
-      <c r="B25" s="29" t="s">
+    <row r="25" spans="2:11" ht="27.75" x14ac:dyDescent="0.7">
+      <c r="B25" s="28" t="s">
         <v>323</v>
       </c>
       <c r="C25" s="10" t="s">
@@ -14780,8 +14786,8 @@
         <v>11189</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="24.75" x14ac:dyDescent="0.6">
-      <c r="B26" s="29" t="s">
+    <row r="26" spans="2:11" ht="27.75" x14ac:dyDescent="0.7">
+      <c r="B26" s="28" t="s">
         <v>324</v>
       </c>
       <c r="C26" s="10" t="s">
@@ -14813,8 +14819,8 @@
         <v>658</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="24.75" x14ac:dyDescent="0.6">
-      <c r="B27" s="29" t="s">
+    <row r="27" spans="2:11" ht="27.75" x14ac:dyDescent="0.7">
+      <c r="B27" s="28" t="s">
         <v>325</v>
       </c>
       <c r="C27" s="10" t="s">
@@ -14846,8 +14852,8 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="24.75" x14ac:dyDescent="0.6">
-      <c r="B28" s="29" t="s">
+    <row r="28" spans="2:11" ht="27.75" x14ac:dyDescent="0.7">
+      <c r="B28" s="28" t="s">
         <v>326</v>
       </c>
       <c r="C28" s="10" t="s">
@@ -14879,8 +14885,8 @@
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="49.5" x14ac:dyDescent="0.6">
-      <c r="B29" s="29" t="s">
+    <row r="29" spans="2:11" ht="55.5" x14ac:dyDescent="0.7">
+      <c r="B29" s="28" t="s">
         <v>327</v>
       </c>
       <c r="C29" s="10" t="s">
